--- a/data/nodes_text.xlsx
+++ b/data/nodes_text.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.armelloni\OneDrive\github\extreme_weather_risk\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\extreme_weather_risk\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9293DD5-7E7E-460D-B33A-06CEC93D7A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{518C90BC-5A41-41B6-A218-7AE79C968F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="72">
   <si>
     <t>node</t>
   </si>
@@ -51,9 +52,6 @@
     <t xml:space="preserve">Fishers  response is coded as Adapt (proactive planning); react (unplanned response); cope (accept passively) (Green et al., 2021). Cope is when fisher prefer to not go out fishing; React is when they apply small modification to their practice, such as fishing in deeper areas or in different time of the day; Adapt is when they take proactive response such as modify their strategy by changing fishing target and/or gear. </t>
   </si>
   <si>
-    <t>technical_solutions</t>
-  </si>
-  <si>
     <t xml:space="preserve">Describes the measures implemented in the case when the strategy is React. The different solutions work differently and have different cost: travel further implies fisherman change fishing location to seek a sheltered place or to find deeper waters; short sets mean that the fisher perform shorter sessions than average (i.e.: reduced soak time for gillnets); other technical includes strategies that are mentioned sporadically (i.e.: use of ice machines). The CPT is compiled manually for each combination of event and fisherman based on what has been mentioned throughout the questionnaire. In case only one strategy is mentioned, this is assigned probability = 1. When two strategies are mentioned, they are 50% probable unless one strategy is explicitly adopted more often than the other (and so on for three strategies). </t>
   </si>
   <si>
@@ -103,6 +101,147 @@
   </si>
   <si>
     <t>stress</t>
+  </si>
+  <si>
+    <t>benefit_personal_community</t>
+  </si>
+  <si>
+    <t>credit</t>
+  </si>
+  <si>
+    <t>entrepeneurship</t>
+  </si>
+  <si>
+    <t>innovative_capacity</t>
+  </si>
+  <si>
+    <t>identity</t>
+  </si>
+  <si>
+    <t>job_mobility</t>
+  </si>
+  <si>
+    <t>benefit_local_community</t>
+  </si>
+  <si>
+    <t>Catches</t>
+  </si>
+  <si>
+    <t>additional_mitigation</t>
+  </si>
+  <si>
+    <t>satisfaction</t>
+  </si>
+  <si>
+    <t>cost</t>
+  </si>
+  <si>
+    <t>profit</t>
+  </si>
+  <si>
+    <t>outdoor_benefit</t>
+  </si>
+  <si>
+    <t>traditional_food</t>
+  </si>
+  <si>
+    <t>knowledge_transmission</t>
+  </si>
+  <si>
+    <t>societal_importance</t>
+  </si>
+  <si>
+    <t>health</t>
+  </si>
+  <si>
+    <t>non_monetary_value</t>
+  </si>
+  <si>
+    <t>societal_risk</t>
+  </si>
+  <si>
+    <t>professional</t>
+  </si>
+  <si>
+    <t>economic_importance</t>
+  </si>
+  <si>
+    <t>economic_risk</t>
+  </si>
+  <si>
+    <t>home</t>
+  </si>
+  <si>
+    <t>individual_importance</t>
+  </si>
+  <si>
+    <t>individual_risk</t>
+  </si>
+  <si>
+    <t>divorced node that summarizes variables related to physical and mental health. All the conditions are necessary to obtain a large value; therefore, we implement the weighted min algorithm (Eq.). Also, the contribution is uneven, with stress contributing 20% less than injury</t>
+  </si>
+  <si>
+    <t>Summarizes variables related to the non-monetary satisfaction derived from the fishing experience. This includes the time spent fishing, the catch amount and the average fish size. All the variables are calculated as relative change. All the conditions are necessary to obtain a large value; therefore, we implement the weighted min algorithm (Eq.). In this case we give equal weight</t>
+  </si>
+  <si>
+    <t>summarizes the outcomes that are not related with money. It depends on the possibility to go out fishing and to obtain satisfying catches, while staying safe. In this case all the conditions are necessary to obtain a large value, therefore we implement the weighted min algorithm (Eq.). The health node is Low-Medium-High; the satisfaction is below-average-more</t>
+  </si>
+  <si>
+    <t>measures how fishing is a source of income. Full-time job; side-job; recreational (or leisure)</t>
+  </si>
+  <si>
+    <t>The extent to which non-fishing income-generating activities are accessible to an individual or household</t>
+  </si>
+  <si>
+    <t>Motivation and capabilities of individuals to explore new technologies and methods for fishing and marketing</t>
+  </si>
+  <si>
+    <t>The possibility to obtain loans for investments</t>
+  </si>
+  <si>
+    <t>The capacity to pursue different avenues (in fishing, marketing, technology, etc.) and to adapt to changing circumstances</t>
+  </si>
+  <si>
+    <t>how important do you consider transmitting your fishing knowledge to future generations</t>
+  </si>
+  <si>
+    <t>how important is fishing to maintain social relations within your community</t>
+  </si>
+  <si>
+    <t>The degree to which fishing contributes to an individual’s sense of identity, including self-perception</t>
+  </si>
+  <si>
+    <t>The extent which an individual value the time spent outdoor (while fishing) to his personal well-being</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The degree to which fishing contributes to build a sense of place/home to a specific location. It can either be at sea or at land </t>
+  </si>
+  <si>
+    <t>label</t>
+  </si>
+  <si>
+    <t>economic aspects related to fishing practices</t>
+  </si>
+  <si>
+    <t>aspects related to the well-being of communities</t>
+  </si>
+  <si>
+    <t>aspects related to the individual well-being and satisfaction</t>
+  </si>
+  <si>
+    <t>Summarizes the importance of the human community dimensions (economic, societal, individual) to different fisherman</t>
+  </si>
+  <si>
+    <t>is your fishing activity contributing to provide for traditional food?</t>
+  </si>
+  <si>
+    <t>a summary of the extra expected price range to reach the fishing grounds, to implement maintenance (after or before the event to adapt to increased risk hazard), to replace the fishing gear</t>
+  </si>
+  <si>
+    <t>relaised catched</t>
+  </si>
+  <si>
+    <t>realised profit</t>
   </si>
 </sst>
 </file>
@@ -138,8 +277,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -420,114 +562,326 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.5546875" customWidth="1"/>
+    <col min="3" max="3" width="158.77734375" style="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="6" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="C6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="8" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>13</v>
       </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="C8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" t="s">
+    </row>
+    <row r="9" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="C9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" t="s">
+    </row>
+    <row r="10" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="C10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B10" t="s">
+    </row>
+    <row r="11" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>21</v>
       </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="C12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B12" t="s">
+    </row>
+    <row r="13" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>25</v>
       </c>
-      <c r="B13" t="s">
-        <v>24</v>
+      <c r="C29" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44670D08-B37D-4FEE-903C-B1674EE72B79}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30.44140625" customWidth="1"/>
+  </cols>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/nodes_text.xlsx
+++ b/data/nodes_text.xlsx
@@ -8,14 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\extreme_weather_risk\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{518C90BC-5A41-41B6-A218-7AE79C968F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA72941D-3067-47DF-87A6-E5007103D6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19310" yWindow="390" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_Hlk205897975" localSheetId="0">Sheet1!$E$34</definedName>
+    <definedName name="_Hlk205898022" localSheetId="0">Sheet1!$E$36</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -26,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="110">
   <si>
     <t>node</t>
   </si>
@@ -58,9 +62,6 @@
     <t>gear</t>
   </si>
   <si>
-    <t xml:space="preserve">Describes the most probable gear used by each fisherman. The CPT is compiled manually for each combination of event and fisherman. In the case when the strategy is cope or react, the CPT reflects what we do expect from the fisher in normal conditions (this can be one or more gears). When the strategy is Adapt, the CPT accounts for what has been mentioned throughout the questionnaire. </t>
-  </si>
-  <si>
     <t>the ability to catch fish depending on gear-fish interactions. For example, a gillnet clogged in algae is more visible and less efficient (less catchability); a gillnet in murky waters is less visible and more efficient (more catchability); the necessity to go to haul the net sooner because of heatwave diminish the soaking time (less catchability). For each combination of species and even the CPT is filled with method M1-bis based on the answer to Q3 (catchability).</t>
   </si>
   <si>
@@ -85,9 +86,6 @@
     <t>damage to the fishing gear ranging from minor to completely losing the fishing gear or part of it because it was lost or irreparably damaged. When the technical solution is no, the CPT is filled with method M1-bis based on the answer to Q10 (damage). When the technical solution is “travel further”, the damage is “no” with probability 1.  With the available answers no other measure is implemented to deal with damages.</t>
   </si>
   <si>
-    <t>Describes the most probable target species associated to each fishing gear. The CPT is compiled manually for each combination of event and gear. In the case when the strategy is cope or react, the CPT reflects what we expect from the fisher in normal conditions (this can be one or more combinations of gear/species). When the strategy is Adapt, the CPT accounts for what has been mentioned throughout the questionnaire. Example: gillnetters normally target a set of species (herring, whitefish, perch), but when there is an heatwave they switch primarily to perch.</t>
-  </si>
-  <si>
     <t>target</t>
   </si>
   <si>
@@ -136,9 +134,6 @@
     <t>cost</t>
   </si>
   <si>
-    <t>profit</t>
-  </si>
-  <si>
     <t>outdoor_benefit</t>
   </si>
   <si>
@@ -235,20 +230,143 @@
     <t>is your fishing activity contributing to provide for traditional food?</t>
   </si>
   <si>
-    <t>a summary of the extra expected price range to reach the fishing grounds, to implement maintenance (after or before the event to adapt to increased risk hazard), to replace the fishing gear</t>
-  </si>
-  <si>
     <t>relaised catched</t>
   </si>
   <si>
-    <t>realised profit</t>
+    <t>group</t>
+  </si>
+  <si>
+    <t>risk</t>
+  </si>
+  <si>
+    <t>individual</t>
+  </si>
+  <si>
+    <t>societal</t>
+  </si>
+  <si>
+    <t>economic</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>operational</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Describes the most probable gear used by each fisherman. The CPT base on literature, when available. The coastal small scale fisherman and the trawlers preferences base on the FDI data of the EU data collection framework. The recreational fisher base on the Fritidsfiske 2024. In the case when the strategy is cope or react, the CPT reflects what we do expect from the fisher in normal conditions (this can be one or more gears). When the strategy is Adapt, the CPT accounts for what has been mentioned throughout the questionnaire. </t>
+  </si>
+  <si>
+    <t>Describes the most probable target species associated to each fishing gear. The CPT base on literature, when available. The coastal small scale fisherman and the trawlers preferences base on the FDI data of the EU data collection framework. The recreational fisher base on the Fritidsfiske 2024. In the case when the strategy is cope or react, the CPT reflects what we expect from the fisher in normal conditions (this can be one or more combinations of gear/species). When the strategy is Adapt, the CPT accounts for what has been mentioned throughout the questionnaire. Example: gillnetters normally target a set of species (herring, whitefish, perch), but when there is an heatwave they switch primarily to perch.</t>
+  </si>
+  <si>
+    <t>Cost represent how large is the expense associated with an extreme weather event compared to the annual expected costs. No is &lt; 0.5%; Low is between 0.5% and 2.5%; Medium is between 2.5% and 5%; high is larger than 5%. The CPT base on literature, when available. The coastal small scale fisherman and the trawlers costs base on the Annual Economic Report data of the EU data collection framework.</t>
+  </si>
+  <si>
+    <t>short_text</t>
+  </si>
+  <si>
+    <t>Describe the presence of adequate infrastructure (harbor, streets) in the area where fishing can potentially happen</t>
+  </si>
+  <si>
+    <t>Modification to fishing practices to counterbalance for bad quality of fish</t>
+  </si>
+  <si>
+    <t>Ability to catch fish depending on gear-fish interactions</t>
+  </si>
+  <si>
+    <t>The real or perceived quality of catches in terms of aspect/health</t>
+  </si>
+  <si>
+    <t>Potential physical damage for operators out of ordinary</t>
+  </si>
+  <si>
+    <t>The decision on whether to go out fishing or not</t>
+  </si>
+  <si>
+    <t>Psychological aspect, including elements such as anxiety and sense of fatigue</t>
+  </si>
+  <si>
+    <t>Distinction between full-time professional; side job and recreational</t>
+  </si>
+  <si>
+    <t>The extent which an individual value the transmission of fishing knowledge and culture to future generations</t>
+  </si>
+  <si>
+    <t>The extent which an individual value fishing to build/maintain social relations within a community</t>
+  </si>
+  <si>
+    <t>The extent which fishing contributes to provide for traditional food</t>
+  </si>
+  <si>
+    <t>The degree to which fishing contributes to build a sense of place/home to a specific location</t>
+  </si>
+  <si>
+    <t>The fishing gear deployed</t>
+  </si>
+  <si>
+    <t>“divorced” node that summarizes variables related to physical and mental health</t>
+  </si>
+  <si>
+    <t>non-monetary satisfaction derived from the fishing experience</t>
+  </si>
+  <si>
+    <t>depends on the possibility to go out fishing and to obtain satisfying catches, while staying safe</t>
+  </si>
+  <si>
+    <t>Describes the most probable target species associated to each fishing gear</t>
+  </si>
+  <si>
+    <t>damage to the fishing gear ranging from minor to completely losing the fishing gear or part of it because it was lost or irreparably damaged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adapt (proactive planning); react (unplanned response); cope (accept passively) </t>
+  </si>
+  <si>
+    <t>how large is the expense associated with an extreme weather event compared to the annual expected costs</t>
+  </si>
+  <si>
+    <t>possibility to change fishing strategy (both gear and target)</t>
+  </si>
+  <si>
+    <t>cycle</t>
+  </si>
+  <si>
+    <t>event</t>
+  </si>
+  <si>
+    <t>fishing_style</t>
+  </si>
+  <si>
+    <t>management</t>
+  </si>
+  <si>
+    <t>stock_status</t>
+  </si>
+  <si>
+    <t>decision</t>
+  </si>
+  <si>
+    <t>Probability associated to extreme weather event</t>
+  </si>
+  <si>
+    <t>Probability associated to fishing style</t>
+  </si>
+  <si>
+    <t>how much fishing regulations allows fishers to implement adaptation strategies</t>
+  </si>
+  <si>
+    <t>the relative status of fish stocks</t>
+  </si>
+  <si>
+    <t>catches obtained</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -256,16 +374,52 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8E8E8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -273,14 +427,60 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -562,310 +762,685 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.5546875" customWidth="1"/>
-    <col min="3" max="3" width="158.77734375" style="1" customWidth="1"/>
+    <col min="2" max="3" width="13.109375" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" customWidth="1"/>
+    <col min="6" max="6" width="154.5546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="8" spans="1:6" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="72" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="9" spans="1:6" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" t="s">
+        <v>90</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11" t="s">
+        <v>73</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" t="s">
+        <v>97</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25" t="s">
+        <v>71</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27" t="s">
+        <v>71</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28" t="s">
+        <v>71</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29" t="s">
+        <v>70</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30" t="s">
+        <v>70</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="D31" t="s">
+        <v>70</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="C32">
+        <v>2</v>
+      </c>
+      <c r="D32" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="1" t="s">
+      <c r="E32" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>45</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>38</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>29</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>47</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F32" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33" t="s">
+        <v>70</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35">
+        <v>2</v>
+      </c>
+      <c r="D35" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+      <c r="D36" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+      <c r="D37" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+      <c r="D38" t="s">
+        <v>68</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39" t="s">
+        <v>68</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
+      <c r="D40" t="s">
+        <v>68</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>48</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>49</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>43</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>46</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>64</v>
+      <c r="F40" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/data/nodes_text.xlsx
+++ b/data/nodes_text.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\extreme_weather_risk\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2016A4F-E0E5-46B5-8709-2676395F9877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4FBB990-2B08-45DC-8BE8-617921540990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-132" yWindow="-132" windowWidth="23304" windowHeight="13944" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_Hlk205897975" localSheetId="0">Sheet1!$E$32</definedName>
-    <definedName name="_Hlk205898022" localSheetId="0">Sheet1!$E$34</definedName>
+    <definedName name="_Hlk205897975" localSheetId="0">Sheet1!$E$36</definedName>
+    <definedName name="_Hlk205898022" localSheetId="0">Sheet1!$E$38</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="156">
   <si>
     <t>node</t>
   </si>
@@ -362,18 +362,12 @@
     <t>Case C3 based on question Q5. The CPT is changed to 100% probability of level _same_ when appropriate technical solutions (i.e.: travel further, ice machine) are mentioned in the narrative</t>
   </si>
   <si>
-    <t>Case C1 based on question Q 3</t>
-  </si>
-  <si>
     <t>Case C4. In the case when the strategy is cope or react, the CPT reflects literature as described in Annex C. When the strategy is React, it is assigned expert based probability based on interviews interpretation</t>
   </si>
   <si>
     <t>Case C4. We interpreted narrative to associate one or more solution to each combination of fisher and MEW. In case only one strategy is mentioned, this is assigned probability = 1. When two or more strategies are mentioned, they are given equal probability unless explicitly indicated in the interviews</t>
   </si>
   <si>
-    <t>Case C3. We interpreted narrative (especially questions Q 2, 4, 13 and 15) to associate one or more among Adapt, React or Cope to each combination of fisher and MEW. The question chosen to fill the CPT depends on the narrative</t>
-  </si>
-  <si>
     <t>Case C4. The CPT reflects literature and interviews as described in Annex C.</t>
   </si>
   <si>
@@ -456,6 +450,55 @@
   </si>
   <si>
     <t>The risk of having economic fluctuations balanced for how economy is considered an important value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The impact of a lost day is not determined by the loss itself, but by its recoverability.
+</t>
+  </si>
+  <si>
+    <t>The impact of a lost day is not determined by the loss itself, but by its recoverability. When value is tied to outcomes, time can be lost and later absorbed. When value is tied to time itself, loss becomes irreversible.</t>
+  </si>
+  <si>
+    <t>objectives_type</t>
+  </si>
+  <si>
+    <t>monetary_loss</t>
+  </si>
+  <si>
+    <t>the severity of monetary losses</t>
+  </si>
+  <si>
+    <t>aware</t>
+  </si>
+  <si>
+    <t>dopes the fisher knows the event ois happening?</t>
+  </si>
+  <si>
+    <t>Describe the awareness of fishers about the event. No awareness implies the fisher performs its activity and is caught by surprise by the event</t>
+  </si>
+  <si>
+    <t>summarise the capability to buffer economic loss</t>
+  </si>
+  <si>
+    <t>Case C1 based on extra question</t>
+  </si>
+  <si>
+    <t>economic_buffers</t>
+  </si>
+  <si>
+    <t>Case C2 with unequal weight, job mobility is 50% less important than credit. Algorithm is wmax</t>
+  </si>
+  <si>
+    <t>Describes the capability to buffer economic loss by obtaining credits or by replacing with other jobs. Only professionals are capable to obtain economic buffers</t>
+  </si>
+  <si>
+    <t>Case C3 based on question Q 3</t>
+  </si>
+  <si>
+    <t>Case C1. We interpreted narrative (especially questions Q 2, 4, 13 and 15) to associate one or more among Adapt, React or Cope to each combination of fisher and MEW. The question chosen to fill the CPT depends on the narrative</t>
+  </si>
+  <si>
+    <t>Case C3. In the case of recreational fishers, if the node go_out is no then the cost is no. For commercial fishers, if the node go_out is no the cost depend on the estimated cost of a missed fishing day balanced on objectives type. When the node go out is yes, loss equal costs</t>
   </si>
 </sst>
 </file>
@@ -478,7 +521,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -494,6 +537,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8E8E8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -534,24 +583,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -834,7 +886,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" style="1" customWidth="1"/>
@@ -912,129 +964,126 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>145</v>
       </c>
       <c r="C5" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>56</v>
+        <v>146</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="117" customHeight="1" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="117" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
@@ -1043,98 +1092,98 @@
         <v>54</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="91.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="64.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="91.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="67.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="64.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C15" s="1">
         <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="64.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="67.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C16" s="1">
         <v>1</v>
@@ -1143,38 +1192,38 @@
         <v>53</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="64.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C17" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>131</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="64.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C18" s="1">
         <v>2</v>
@@ -1183,119 +1232,115 @@
         <v>53</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="G18" s="1" t="s">
+      <c r="F19" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+    <row r="20" spans="1:8" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C20" s="1">
         <v>1</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="1">
-        <v>2</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>52</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C21" s="1">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F20" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="G20" s="1" t="s">
+      <c r="F22" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" s="1">
-        <v>2</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="1">
-        <v>2</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>15</v>
+        <v>143</v>
       </c>
       <c r="C23" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>89</v>
+      <c r="E23" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="H23" s="1"/>
+        <v>155</v>
+      </c>
     </row>
     <row r="24" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C24" s="1">
         <v>2</v>
@@ -1303,19 +1348,19 @@
       <c r="D24" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>136</v>
+      <c r="E24" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>135</v>
+        <v>38</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C25" s="1">
         <v>2</v>
@@ -1324,18 +1369,18 @@
         <v>52</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>2</v>
@@ -1343,99 +1388,100 @@
       <c r="D26" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>84</v>
+      <c r="E26" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+      <c r="H26" s="1"/>
+    </row>
+    <row r="27" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C27" s="1">
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>63</v>
+        <v>134</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>133</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C28" s="1">
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>137</v>
+        <v>36</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C29" s="1">
         <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>65</v>
+        <v>84</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>90</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="C30" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>40</v>
+        <v>148</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>97</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C31" s="1">
         <v>2</v>
@@ -1444,153 +1490,233 @@
         <v>51</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>88</v>
+        <v>63</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C32" s="1">
         <v>2</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>41</v>
+        <v>64</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C33" s="1">
         <v>2</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>43</v>
+        <v>65</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C34" s="1">
         <v>2</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C35" s="1">
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>84</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="1">
+        <v>2</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="1">
+        <v>2</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" s="1">
+        <v>2</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="1">
+        <v>2</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="1">
-        <v>2</v>
-      </c>
-      <c r="D36" s="1" t="s">
+      <c r="C40" s="1">
+        <v>2</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E40" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F36" s="6" t="s">
+      <c r="F40" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="1">
+        <v>2</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42" s="1">
+        <v>2</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F42" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="G36" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C37" s="1">
-        <v>2</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38" s="1">
-        <v>2</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>119</v>
+      <c r="G42" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/data/nodes_text.xlsx
+++ b/data/nodes_text.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\extreme_weather_risk\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4FBB990-2B08-45DC-8BE8-617921540990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA914B8-C9E9-4A43-90BD-11311069557C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-132" yWindow="-132" windowWidth="23304" windowHeight="13944" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,9 +41,6 @@
     <t>infrastructure</t>
   </si>
   <si>
-    <t>strategy</t>
-  </si>
-  <si>
     <t>gear</t>
   </si>
   <si>
@@ -62,9 +59,6 @@
     <t>target</t>
   </si>
   <si>
-    <t>go_out</t>
-  </si>
-  <si>
     <t>stress</t>
   </si>
   <si>
@@ -98,9 +92,6 @@
     <t>satisfaction</t>
   </si>
   <si>
-    <t>cost</t>
-  </si>
-  <si>
     <t>outdoor_benefit</t>
   </si>
   <si>
@@ -131,9 +122,6 @@
     <t>economic_risk</t>
   </si>
   <si>
-    <t>home</t>
-  </si>
-  <si>
     <t>individual_importance</t>
   </si>
   <si>
@@ -258,9 +246,6 @@
   </si>
   <si>
     <t>cycle</t>
-  </si>
-  <si>
-    <t>event</t>
   </si>
   <si>
     <t>fishing_style</t>
@@ -459,18 +444,12 @@
     <t>The impact of a lost day is not determined by the loss itself, but by its recoverability. When value is tied to outcomes, time can be lost and later absorbed. When value is tied to time itself, loss becomes irreversible.</t>
   </si>
   <si>
-    <t>objectives_type</t>
-  </si>
-  <si>
     <t>monetary_loss</t>
   </si>
   <si>
     <t>the severity of monetary losses</t>
   </si>
   <si>
-    <t>aware</t>
-  </si>
-  <si>
     <t>dopes the fisher knows the event ois happening?</t>
   </si>
   <si>
@@ -499,6 +478,27 @@
   </si>
   <si>
     <t>Case C3. In the case of recreational fishers, if the node go_out is no then the cost is no. For commercial fishers, if the node go_out is no the cost depend on the estimated cost of a missed fishing day balanced on objectives type. When the node go out is yes, loss equal costs</t>
+  </si>
+  <si>
+    <t>aware_of_event</t>
+  </si>
+  <si>
+    <t>extreme_event</t>
+  </si>
+  <si>
+    <t>go_fishing</t>
+  </si>
+  <si>
+    <t>costs</t>
+  </si>
+  <si>
+    <t>substitution_capacity</t>
+  </si>
+  <si>
+    <t>sense_of_home</t>
+  </si>
+  <si>
+    <t>strategy_to_change</t>
   </si>
 </sst>
 </file>
@@ -889,7 +889,7 @@
   <dimension ref="A1:H42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="28.21875" style="1" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="5.33203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="13.5546875" style="1" customWidth="1"/>
@@ -904,81 +904,81 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>76</v>
+        <v>150</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
@@ -989,734 +989,734 @@
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="117" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>3</v>
+        <v>155</v>
       </c>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" s="1">
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" s="1">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" s="1">
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="F10" s="6" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C12" s="1">
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="1">
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="91.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" s="1">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="64.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>10</v>
+        <v>151</v>
       </c>
       <c r="C15" s="1">
         <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="67.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" s="1">
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="64.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C17" s="1">
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="64.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C18" s="1">
         <v>2</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C19" s="1">
         <v>2</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>22</v>
+        <v>152</v>
       </c>
       <c r="C20" s="1">
         <v>1</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C21" s="1">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C22" s="1">
         <v>2</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C23" s="1">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C24" s="1">
         <v>2</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C25" s="1">
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C26" s="1">
         <v>2</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H26" s="1"/>
     </row>
     <row r="27" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C27" s="1">
         <v>2</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C28" s="1">
         <v>2</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C29" s="1">
         <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C30" s="1">
         <v>4</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C31" s="1">
         <v>2</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C32" s="1">
         <v>2</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C33" s="1">
         <v>2</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C34" s="1">
         <v>2</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C35" s="1">
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C36" s="1">
         <v>2</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>33</v>
+        <v>154</v>
       </c>
       <c r="C37" s="1">
         <v>2</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C38" s="1">
         <v>2</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C39" s="1">
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C40" s="1">
         <v>2</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C41" s="1">
         <v>2</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C42" s="1">
         <v>2</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
